--- a/out/Attention-mamba2_repeat_2_000001.xlsx
+++ b/out/Attention-mamba2_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5903981995424215</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.228705708809411</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.2554444171274073</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.2554444171274073</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5903981995424215</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.190398199542422</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.190398199542422</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.901262215535431</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.901262215535431</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.2554444171274073</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-0.0004127109979488887</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.1777013731018318</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.2554444171274073</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.3558769841857609</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.686554382243041</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>1.551738803477122</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.211187976603924</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.50126221553543</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>1.28669125452937</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.04285140484154346</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.2554444171274073</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>1.160876117986484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.03711122103292708</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.190398199542422</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001896032321299426</v>
+        <v>1.192200085307919</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.01814283371088052</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.005172185184510192</v>
+        <v>1.191326645633626</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.008658513109615958</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.01526345635953965</v>
+        <v>1.190476663351405</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>-0.05164624914387304</v>
+        <v>0.003604152246312667</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05184846599912434</v>
+        <v>1.189016508269457</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.002495987299174661</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05203172212692618</v>
+        <v>1.190401835150819</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.03728469143998202</v>
+        <v>0.001039389265359948</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08931641356690821</v>
+        <v>1.189981135130481</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.000536219004996832</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08931641356690821</v>
+        <v>1.190013764300718</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>0.0002075699550123441</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08945084152678144</v>
+        <v>1.189891904863847</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003461520480537919</v>
+        <v>0.0001112445520511855</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.07690178879500693</v>
+        <v>1.189906061485364</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>5.203184495101626e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.07898211856920447</v>
+        <v>1.189899314479759</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>2.217410639548993e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08991349340107269</v>
+        <v>1.189890999149842</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>6.529296331733944e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1150725442700547</v>
+        <v>1.189882311626848</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-0.04400913803276717</v>
+        <v>3.742348189881177e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.1331753303741987</v>
+        <v>1.189876053911075</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-3.09281402832566e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.1333497809989354</v>
+        <v>1.18986980454364</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-0.0583617855941025</v>
+        <v>-4.452445000690905e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.1917115665930379</v>
+        <v>1.18986385353288</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.555348042317843e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.1918755595193687</v>
+        <v>1.189859011225438</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.004881285253856503</v>
+        <v>-4.737866375420875e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1738777586190541</v>
+        <v>1.18985409002389</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.176506554746662</v>
+        <v>1.189854082052795</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.03151345862418916</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.1237455380335983</v>
+        <v>1.189854241474684</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00782035532453317</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.1397437696468864</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.01846002281726574</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.1106727375570749</v>
+        <v>1.189854496549707</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.004104596566161738</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.120968074467589</v>
+        <v>1.189854249445779</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00163668255659257</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.1218120004338714</v>
+        <v>1.189854209590306</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004850084855597275</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.1224844527821465</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0004261362432586212</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.1221196032017417</v>
+        <v>1.189854217561401</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0.0001174785315340894</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.1223121829184521</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0.000123410687185425</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.1221832914117758</v>
+        <v>1.189854249445779</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.035423691953307e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.1221265129143447</v>
+        <v>1.189854345098912</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.221227785843479e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.122152422773688</v>
+        <v>1.189854281330157</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>1.038171962443557e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.1221640078485942</v>
+        <v>1.189854241474684</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>1.806540613632449e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.122171012424875</v>
+        <v>1.189854217561401</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-8.312562932979024e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.1221861752154651</v>
+        <v>1.189853970457473</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.1223749782888866</v>
+        <v>1.189853890746528</v>
       </c>
     </row>
     <row r="81">
@@ -65328,21 +65328,21 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0.031569485230203</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.09080549305868359</v>
+        <v>1.189853938573095</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.09080549305868359</v>
+        <v>1.189854058139512</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.09094921732429088</v>
+        <v>1.189854042197323</v>
       </c>
     </row>
     <row r="84">
@@ -67713,21 +67713,21 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>7.347392288238707e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.08452786667428701</v>
+        <v>1.189854058139512</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.09093254845698225</v>
+        <v>1.189854042197323</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.00115594826300748</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.05984344264994038</v>
+        <v>1.189854097994984</v>
       </c>
     </row>
     <row r="87">
@@ -70098,21 +70098,21 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.02931484968947411</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.0604617505045007</v>
+        <v>1.189854097994984</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.06061191263548588</v>
+        <v>1.189854097994984</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.02932778426171712</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.001686553906540736</v>
+        <v>1.189854249445779</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.03566209544168816</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.04020679317920993</v>
+        <v>1.189854464665329</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.01355377464393029</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03156227338462323</v>
+        <v>1.18985437698329</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.005610193701444624</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.0291889855443131</v>
+        <v>1.189854329156723</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.003387212079559179</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03033698965227651</v>
+        <v>1.18985437698329</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0.0005728216941772416</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.02808621852664149</v>
+        <v>1.189854193648118</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0.0003082726652513318</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.02812671024457121</v>
+        <v>1.189854201619212</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0.0001637935876340652</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.02814444149730261</v>
+        <v>1.189854209590306</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>8.541617088159809e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.02815080035332043</v>
+        <v>1.189854217561401</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>4.026733588043313e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.0281453933179396</v>
+        <v>1.189854217561401</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>2.523692827618356e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.02815540545579535</v>
+        <v>1.189854257416873</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>1.60900720277718e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.02816247224889335</v>
+        <v>1.189854321185629</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>1.100618398017284e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.02816812185739575</v>
+        <v>1.189854432780951</v>
       </c>
     </row>
     <row r="102">
@@ -82023,7 +82023,7 @@
         <v>0</v>
       </c>
       <c r="IY102" t="n">
-        <v>4.149552187342177e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.02816538438396878</v>
+        <v>1.189854480607518</v>
       </c>
     </row>
     <row r="103">
@@ -82818,7 +82818,7 @@
         <v>0</v>
       </c>
       <c r="IY103" t="n">
-        <v>-9.029156551854776e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.02815941185223649</v>
+        <v>1.189854440752046</v>
       </c>
     </row>
     <row r="104">
@@ -83613,7 +83613,7 @@
         <v>0</v>
       </c>
       <c r="IY104" t="n">
-        <v>-3.381380401563642e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.02815354349036305</v>
+        <v>1.189854369012196</v>
       </c>
     </row>
     <row r="105">
@@ -84408,7 +84408,7 @@
         <v>0</v>
       </c>
       <c r="IY105" t="n">
-        <v>-3.832421389139401e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.02814925671658968</v>
+        <v>1.189854488578613</v>
       </c>
     </row>
     <row r="106">
@@ -85203,7 +85203,7 @@
         <v>0</v>
       </c>
       <c r="IY106" t="n">
-        <v>-4.770037712665319e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.02814377725147002</v>
+        <v>1.189854329156723</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.02790430444590282</v>
+        <v>1.189854097994984</v>
       </c>
     </row>
     <row r="108">
@@ -86793,21 +86793,21 @@
         <v>0</v>
       </c>
       <c r="IY108" t="n">
-        <v>-0.007932144378072509</v>
+        <v>0</v>
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.002024664958185284</v>
+        <v>1.189854050168417</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-0.007851378082460846</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.01212078198536951</v>
+        <v>1.189854082052795</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0119521554141615</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="111">
@@ -89178,21 +89178,21 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>-0.0005058797136242252</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.01144627570053726</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.01144627570053726</v>
+        <v>1.189854066110606</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.01144627570053726</v>
+        <v>1.18985394654419</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.01144627570053726</v>
+        <v>1.189853906688717</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.01127638286941708</v>
+        <v>1.189854050168417</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.03164745504920725</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.07487419251132757</v>
+        <v>1.189854185677023</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.01394712200957578</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.07096676438465994</v>
+        <v>1.189854169734834</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.005566106868517128</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.0680754364058678</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.06556878941017202</v>
+        <v>1.189854105966079</v>
       </c>
     </row>
     <row r="120">
@@ -96333,21 +96333,21 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>-0.04528613314120617</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.01699360733029479</v>
+        <v>1.189854002341851</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.01674915781991894</v>
+        <v>1.189853882775434</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.0523920228013491</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1219791346191778</v>
+        <v>1.189854002341851</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.03674766765798164</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1428754997742784</v>
+        <v>1.189854050168417</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.02892554936495987</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1638754696276479</v>
+        <v>1.189854145821551</v>
       </c>
     </row>
     <row r="125">
@@ -100308,7 +100308,7 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>0.007867952472499223</v>
+        <v>0</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.150608168761133</v>
+        <v>1.189854026255134</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.008307757680373387</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.190398199542422</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1510192999081192</v>
+        <v>1.189854034226228</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000001.xlsx
+++ b/out/Attention-mamba2_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.4894390911976032</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.50126221553543</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636436</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.6427717100636433</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.6427717100636433</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.50126221553543</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636436</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-3.704026282858103e-05</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.01222984706196723</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001896032321299426</v>
+        <v>0.0244969722668915</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.005791623352764841</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.005172185184510192</v>
+        <v>0.02381286253738136</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.002571066569737771</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.01526345635953965</v>
+        <v>0.02314603865269839</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>-0.05164624914387304</v>
+        <v>0.0007171590920566167</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.05184846599912434</v>
+        <v>0.02200124573180766</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0009018662536843695</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.05203172212692618</v>
+        <v>0.02308525946501945</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.03728469143998202</v>
+        <v>0.0002866036517400968</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08931641356690821</v>
+        <v>0.02275470112811949</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.000156083433952091</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.901262215535431</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08931641356690821</v>
+        <v>0.02277918179252115</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>2.998639431021819e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08945084152678144</v>
+        <v>0.02268268285992474</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003461520480537919</v>
+        <v>2.014367954916856e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.07690178879500693</v>
+        <v>0.0226926873073196</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>6.863810797240234e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.07898211856920447</v>
+        <v>0.02268631910131173</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-2.668518548882899e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08991349340107269</v>
+        <v>0.02267871884255274</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1150725442700547</v>
+        <v>0.02250771001106687</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-0.04400913803276717</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.1331753303741987</v>
+        <v>0.005739711703876034</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-0.05201813547952598</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.1333497809989354</v>
+        <v>-0.02951980347465526</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-0.0583617855941025</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.1917115665930379</v>
+        <v>-0.02968096863062726</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.0006227909712531925</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.1918755595193687</v>
+        <v>-0.01082720852940041</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.004881285253856503</v>
+        <v>0.01797005561514052</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1738777586190541</v>
+        <v>0.007142886941212113</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.008074883969136307</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.176506554746662</v>
+        <v>0.005190715968353325</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.03151345862418916</v>
+        <v>0.01313915832357821</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.1237455380335983</v>
+        <v>0.02334351734379877</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00782035532453317</v>
+        <v>0.003839053668407449</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.1397437696468864</v>
+        <v>0.01783916495775001</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.01846002281726574</v>
+        <v>0.006925732481915595</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.1106727375570749</v>
+        <v>0.02784146091329097</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.004104596566161738</v>
+        <v>0.00169619351263881</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.120968074467589</v>
+        <v>0.02429622140765155</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.00163668255659257</v>
+        <v>0.000703443244969089</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.1218120004338714</v>
+        <v>0.0240025604464988</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004850084855597275</v>
+        <v>0.0002354036017903214</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.1224844527821465</v>
+        <v>0.02376790063683165</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0004261362432586212</v>
+        <v>0.0001791213460764917</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.1221196032017417</v>
+        <v>0.02389014822392911</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0.0001174785315340894</v>
+        <v>5.513453273658291e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.1223121829184521</v>
+        <v>0.02382057498382393</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0.000123410687185425</v>
+        <v>4.808047478920592e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.1221832914117758</v>
+        <v>0.02386164886658197</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.035423691953307e-05</v>
+        <v>3.235954708645441e-05</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.1221265129143447</v>
+        <v>0.02387793868723512</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>3.221227785843479e-05</v>
+        <v>1.011300848509822e-05</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.122152422773688</v>
+        <v>0.02386573263122956</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>1.038171962443557e-05</v>
+        <v>1.441890161883788e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.1221640078485942</v>
+        <v>0.02385847008624009</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>1.806540613632449e-06</v>
+        <v>-2.113439143257689e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.122171012424875</v>
+        <v>0.02385278559677839</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-8.312562932979024e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.1221861752154651</v>
+        <v>0.02367114776789141</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-0.04479491687243914</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.1223749782888866</v>
+        <v>-0.02112321112793544</v>
       </c>
     </row>
     <row r="81">
@@ -65328,21 +65328,21 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0.031569485230203</v>
+        <v>0</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.09080549305868359</v>
+        <v>-0.02114085878098151</v>
       </c>
     </row>
     <row r="82">
@@ -66123,21 +66123,21 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0</v>
+        <v>0.003433365730467977</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.09080549305868359</v>
+        <v>-0.01424245828833315</v>
       </c>
     </row>
     <row r="83">
@@ -66918,21 +66918,21 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0</v>
+        <v>0.001484124653707498</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.09094921732429088</v>
+        <v>-0.01472185333319462</v>
       </c>
     </row>
     <row r="84">
@@ -67713,21 +67713,21 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>7.347392288238707e-05</v>
+        <v>0.0008549248842026155</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.08452786667428701</v>
+        <v>-0.0145021848220583</v>
       </c>
     </row>
     <row r="85">
@@ -68508,21 +68508,21 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0</v>
+        <v>0.0003672297788632544</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.09093254845698225</v>
+        <v>-0.01462578315572324</v>
       </c>
     </row>
     <row r="86">
@@ -69303,21 +69303,21 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.00115594826300748</v>
+        <v>0.000282043194435871</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.05984344264994038</v>
+        <v>-0.01443029807603895</v>
       </c>
     </row>
     <row r="87">
@@ -70098,21 +70098,21 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.02931484968947411</v>
+        <v>0.0001386008471335721</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.50126221553543</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.0604617505045007</v>
+        <v>-0.014436133460538</v>
       </c>
     </row>
     <row r="88">
@@ -70893,21 +70893,21 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0</v>
+        <v>6.680042356678607e-05</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.06061191263548588</v>
+        <v>-0.01444155115278752</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.02932778426171712</v>
+        <v>6.500776802759109e-05</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.001686553906540736</v>
+        <v>-0.01437819340131339</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.03566209544168816</v>
+        <v>5.429450944315157e-05</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.04020679317920993</v>
+        <v>-0.01433449247640884</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.01355377464393029</v>
+        <v>1.991774103205633e-05</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03156227338462323</v>
+        <v>-0.014349559868966</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.005610193701444624</v>
+        <v>5.902756943510027e-06</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.0291889855443131</v>
+        <v>-0.01435731956792856</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.003387212079559179</v>
+        <v>1.120146920154187e-06</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03033698965227651</v>
+        <v>-0.01436095019330725</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0.0005728216941772416</v>
+        <v>-3.221732732688002e-06</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.02808621852664149</v>
+        <v>-0.01436870747878822</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0.0003082726652513318</v>
+        <v>-3.952001159231278e-06</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.02812671024457121</v>
+        <v>-0.0143736478956606</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0.0001637935876340652</v>
+        <v>-4.460077521320422e-06</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.02814444149730261</v>
+        <v>-0.01437861812322738</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>8.541617088159809e-05</v>
+        <v>-4.722077231512602e-06</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.02815080035332043</v>
+        <v>-0.01438360324657615</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>4.026733588043313e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.0281453933179396</v>
+        <v>-0.01438360324657615</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>2.523692827618356e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.02815540545579535</v>
+        <v>-0.01438356339110376</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>1.60900720277718e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.5705587654005176</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.02816247224889335</v>
+        <v>-0.01438349962234811</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>1.100618398017284e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.02816812185739575</v>
+        <v>-0.01438338802702562</v>
       </c>
     </row>
     <row r="102">
@@ -82023,7 +82023,7 @@
         <v>0</v>
       </c>
       <c r="IY102" t="n">
-        <v>4.149552187342177e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.02816538438396878</v>
+        <v>-0.01438334020045889</v>
       </c>
     </row>
     <row r="103">
@@ -82818,7 +82818,7 @@
         <v>0</v>
       </c>
       <c r="IY103" t="n">
-        <v>-9.029156551854776e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.02815941185223649</v>
+        <v>-0.01438338005593116</v>
       </c>
     </row>
     <row r="104">
@@ -83613,7 +83613,7 @@
         <v>0</v>
       </c>
       <c r="IY104" t="n">
-        <v>-3.381380401563642e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.02815354349036305</v>
+        <v>-0.01438345179578138</v>
       </c>
     </row>
     <row r="105">
@@ -84408,7 +84408,7 @@
         <v>0</v>
       </c>
       <c r="IY105" t="n">
-        <v>-3.832421389139401e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.02814925671658968</v>
+        <v>-0.01438333222936443</v>
       </c>
     </row>
     <row r="106">
@@ -85203,7 +85203,7 @@
         <v>0</v>
       </c>
       <c r="IY106" t="n">
-        <v>-4.770037712665319e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.02814377725147002</v>
+        <v>-0.01438349165125366</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.02790430444590282</v>
+        <v>-0.01438372281299299</v>
       </c>
     </row>
     <row r="108">
@@ -86793,21 +86793,21 @@
         <v>0</v>
       </c>
       <c r="IY108" t="n">
-        <v>-0.007932144378072509</v>
+        <v>0</v>
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.002024664958185284</v>
+        <v>-0.01438377063955984</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-0.007851378082460846</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.01212078198536951</v>
+        <v>-0.0143837387551819</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0119521554141615</v>
+        <v>-0.01438367498642625</v>
       </c>
     </row>
     <row r="111">
@@ -89178,21 +89178,21 @@
         <v>0</v>
       </c>
       <c r="IY111" t="n">
-        <v>-0.0005058797136242252</v>
+        <v>0</v>
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636434</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.01144627570053726</v>
+        <v>-0.01438367498642625</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.01144627570053726</v>
+        <v>-0.01438375469737081</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>0</v>
+        <v>-4.992769222531319e-06</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.50126221553543</v>
+        <v>-1.549436947795724</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.01144627570053726</v>
+        <v>-0.0143888750041048</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-2.50126221553543</v>
+        <v>-0.8427717100636436</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.01144627570053726</v>
+        <v>-0.01439515449558094</v>
       </c>
     </row>
     <row r="115">
@@ -92358,21 +92358,21 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0</v>
+        <v>0.0007855151347449503</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5903981995424215</v>
+        <v>-0.1361064723315629</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.01127638286941708</v>
+        <v>-0.0128143313820879</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.03164745504920725</v>
+        <v>0.0007652300134117918</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.190398199542422</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.07487419251132757</v>
+        <v>-0.0120710537628216</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.01394712200957578</v>
+        <v>0.0003581846284235919</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.6427717100636433</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.07096676438465994</v>
+        <v>-0.01212164280054509</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.005566106868517128</v>
+        <v>0.0001600402951139165</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.901262215535431</v>
+        <v>-0.6427717100636433</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.0680754364058678</v>
+        <v>-0.0121604653700433</v>
       </c>
     </row>
     <row r="119">
@@ -95538,21 +95538,21 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0</v>
+        <v>6.362762543959252e-05</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.5903981995424215</v>
+        <v>0.0638935276684371</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.06556878941017202</v>
+        <v>-0.01219340755399817</v>
       </c>
     </row>
     <row r="120">
@@ -96333,21 +96333,21 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>-0.04528613314120617</v>
+        <v>1.140833366682302e-05</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.01699360733029479</v>
+        <v>-0.01223450481954578</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.01674915781991894</v>
+        <v>-0.01244378192724951</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.0523920228013491</v>
+        <v>0.04040284841532848</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1219791346191778</v>
+        <v>0.06871009922362283</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.03674766765798164</v>
+        <v>0.02833904925417758</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1428754997742784</v>
+        <v>0.08482550302227121</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.02892554936495987</v>
+        <v>0.022306959490142</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1638754696276479</v>
+        <v>0.1010207713046549</v>
       </c>
     </row>
     <row r="125">
@@ -100308,7 +100308,7 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>0.007867952472499223</v>
+        <v>0.006067602199339704</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.150608168761133</v>
+        <v>0.09078895699654869</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.008307757680373387</v>
+        <v>0.006405674593389435</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.190398199542422</v>
+        <v>0.7705587654005177</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1510192999081192</v>
+        <v>0.09110552368682599</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000001.xlsx
+++ b/out/Attention-mamba2_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02085027098655701</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4894390911976032</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1831559538841248</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.2999999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.04311823099851608</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.06485386192798615</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.04271537810564041</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.3013719320297241</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.06413553655147552</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.05619759857654572</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.01271563023328781</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.07160837948322296</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.03612445294857025</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.06658336520195007</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.02548615634441376</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2377505153417587</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.372608482837677</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.4112226963043213</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0059819296002388</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.08042165637016296</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.04262510314583778</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8427717100636436</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.05348653346300125</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.05478795617818832</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.03523834049701691</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1570518910884857</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6427717100636433</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2384156137704849</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6427717100636433</v>
+        <v>0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.04484488070011139</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0259803980588913</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7705587654005177</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.03047862648963928</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7705587654005177</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0708463042974472</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.03683719038963318</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.4481849372386932</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.07608968019485474</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8427717100636434</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.1158312782645226</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0654134601354599</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.04499118030071259</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.05896298587322235</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.03423741459846497</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.02798718214035034</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.03064344823360443</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.3803468644618988</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.241810530424118</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.1723001599311829</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.1150992885231972</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-2.975905342493206e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.01281327730767792</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.07241015881299973</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.02566096483563806</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.04950529396035906</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.08281875401735306</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.1118908286762438</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.01522759692281715</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.07068553566932678</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.09277907819874584</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.003086838631631702</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.08051518350839615</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8427717100636436</v>
+        <v>0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>-3.704026282858103e-05</v>
+        <v>0.08370368467059662</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01222984706196723</v>
+        <v>0.002672618539613283</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.05367901921272278</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.0244969722668915</v>
+        <v>0.08595893670423399</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.005791623352764841</v>
+        <v>0.001304033150794584</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02870155870914459</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.02381286253738136</v>
+        <v>0.08589162276396481</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002571066569737771</v>
+        <v>0.0006197404563852321</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.07046616077423096</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.02314603865269839</v>
+        <v>0.08582568967481796</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0007171590920566167</v>
+        <v>0.0002549836648199931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.09345868229866028</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.02200124573180766</v>
+        <v>0.08571575663521513</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0009018662536843695</v>
+        <v>0.0001755711286661125</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.1272715479135513</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.02308525946501945</v>
+        <v>0.0858111226114151</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002866036517400968</v>
+        <v>7.038158176873161e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02761002629995346</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.02275470112811949</v>
+        <v>0.08577611835331517</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.000156083433952091</v>
+        <v>3.375395344421761e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0294090136885643</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.02277918179252115</v>
+        <v>0.08577383498870163</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>2.998639431021819e-05</v>
+        <v>1.022105850705674e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.1143838465213776</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.02268268285992474</v>
+        <v>0.08576033407009277</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.014367954916856e-05</v>
+        <v>3.589498920038333e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.1178103387355804</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5705587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.0226926873073196</v>
+        <v>0.085756749583998</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.863810797240234e-06</v>
+        <v>-1.047297874682042e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.04790331423282623</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.02268631910131173</v>
+        <v>0.08575162108575948</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.668518548882899e-07</v>
+        <v>-2.868697537608634e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.06429532170295715</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.02267871884255274</v>
+        <v>0.08574636105988361</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-4.077656293461284e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.08470404148101807</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.02250771001106687</v>
+        <v>0.08574107179723191</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.09840543568134308</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.005739711703876034</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.05201813547952598</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.1216852515935898</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.02951980347465526</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.116411030292511</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.02968096863062726</v>
+        <v>0.08573574388812552</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006227909712531925</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.1018993258476257</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.01082720852940041</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01797005561514052</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.100235715508461</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.007142886941212113</v>
+        <v>0.08573582359907007</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008074883969136307</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.1066407263278961</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5705587654005176</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.005190715968353325</v>
+        <v>0.08573581562797562</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01313915832357821</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.1270077228546143</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5705587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.02334351734379877</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003839053668407449</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0304449275135994</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5705587654005176</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.01783916495775001</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006925732481915595</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.08147308230400085</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5705587654005176</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.02784146091329097</v>
+        <v>0.08573623012488754</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00169619351263881</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.1258122026920319</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.5705587654005176</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.02429622140765155</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.000703443244969089</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.09181785583496094</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.5705587654005176</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.0240025604464988</v>
+        <v>0.08573594316548691</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002354036017903214</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.09137147665023804</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.5705587654005176</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.02376790063683165</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001791213460764917</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.08633142709732056</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5705587654005176</v>
+        <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.02389014822392911</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.513453273658291e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.1124690920114517</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.02382057498382393</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>4.808047478920592e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.03986454755067825</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.02386164886658197</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.235954708645441e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02382677048444748</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.02387793868723512</v>
+        <v>0.08573607867409289</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.011300848509822e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.1165706962347031</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.02386573263122956</v>
+        <v>0.08573601490533701</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>1.441890161883788e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.03962594270706177</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5705587654005176</v>
+        <v>-0.3</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.02385847008624009</v>
+        <v>0.08573597504986473</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.113439143257689e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.1084654033184052</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7705587654005177</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.02385278559677839</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.1023992598056793</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7705587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.02367114776789141</v>
+        <v>0.08573570403265325</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.04479491687243914</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.006118275225162506</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.02112321112793544</v>
+        <v>0.08573562432170846</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004271037876605988</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.02114085878098151</v>
+        <v>0.08573567214827518</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.003433365730467977</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.01938682794570923</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.01424245828833315</v>
+        <v>0.08573579171469226</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.001484124653707498</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.03338298946619034</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.01472185333319462</v>
+        <v>0.08573577577250334</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.0008549248842026155</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.03522747009992599</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.5705587654005176</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.0145021848220583</v>
+        <v>0.08573579171469226</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.0003672297788632544</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.06255679577589035</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7705587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>-0.01462578315572324</v>
+        <v>0.08573577577250334</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.000282043194435871</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.05047409236431122</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>-0.01443029807603895</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.0001386008471335721</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006545256823301315</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>-0.014436133460538</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>6.680042356678607e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.09575867652893066</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>-0.01444155115278752</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>6.500776802759109e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.07868045568466187</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.01437819340131339</v>
+        <v>0.08573598302095919</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>5.429450944315157e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.05306160449981689</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.01433449247640884</v>
+        <v>0.08573619824050972</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>1.991774103205633e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.07530277967453003</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.014349559868966</v>
+        <v>0.0857361105584707</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>5.902756943510027e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.04822862893342972</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.01435731956792856</v>
+        <v>0.08573606273190398</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>1.120146920154187e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.1112610697746277</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.01436095019330725</v>
+        <v>0.0857361105584707</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>-3.221732732688002e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02487679570913315</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.01436870747878822</v>
+        <v>0.08573592722329799</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>-3.952001159231278e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.005148991942405701</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.0143736478956606</v>
+        <v>0.08573593519439246</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-4.460077521320422e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.03896266222000122</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.01437861812322738</v>
+        <v>0.08573594316548691</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-4.722077231512602e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.006210658699274063</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.01438360324657615</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01430939882993698</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.01438360324657615</v>
+        <v>0.08573595113658136</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.1204110383987427</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1361064723315629</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.01438356339110376</v>
+        <v>0.08573599099205365</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.1240293830633163</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5705587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.01438349962234811</v>
+        <v>0.08573605476080952</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.1225882768630981</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.01438338802702562</v>
+        <v>0.0857361663561319</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.07113641500473022</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.01438334020045889</v>
+        <v>0.08573621418269864</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.1047483831644058</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.01438338005593116</v>
+        <v>0.08573617432722636</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.1180445849895477</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.01438345179578138</v>
+        <v>0.08573610258737625</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.1306850612163544</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.01438333222936443</v>
+        <v>0.08573622215379309</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.08124767243862152</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.01438349165125366</v>
+        <v>0.08573606273190398</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.1038160175085068</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7705587654005177</v>
+        <v>-0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.01438372281299299</v>
+        <v>0.08573583157016454</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06852950155735016</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.01438377063955984</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002210322767496109</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.0143837387551819</v>
+        <v>0.08573581562797562</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.04770264029502869</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.01438367498642625</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002155490219593048</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8427717100636434</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.01438367498642625</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.01735235005617142</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.01438375469737081</v>
+        <v>0.08573579968578671</v>
       </c>
     </row>
     <row r="113">
@@ -90768,21 +90768,21 @@
         <v>0</v>
       </c>
       <c r="IY113" t="n">
-        <v>-4.992769222531319e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002108506858348846</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.549436947795724</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.0143888750041048</v>
+        <v>0.08573568011936965</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01085083559155464</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8427717100636436</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.01439515449558094</v>
+        <v>0.08573564026389736</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.0007855151347449503</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.04032652080059052</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1361064723315629</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.0128143313820879</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.0007652300134117918</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.02152110636234283</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.0638935276684371</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.0120710537628216</v>
+        <v>0.08573591925220354</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.0003581846284235919</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.01768418028950691</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6427717100636433</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.01212164280054509</v>
+        <v>0.08573590331001463</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.0001600402951139165</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.009849186986684799</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6427717100636433</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.0121604653700433</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>6.362762543959252e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.007919818162918091</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.0638935276684371</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.01219340755399817</v>
+        <v>0.08573583954125899</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>1.140833366682302e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.1233797669410706</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.01223450481954578</v>
+        <v>0.08573573591703107</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.08949634432792664</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.01244378192724951</v>
+        <v>0.085735616350614</v>
       </c>
     </row>
     <row r="122">
@@ -97923,7 +97923,7 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>0.04040284841532848</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.05687950551509857</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.06871009922362283</v>
+        <v>0.08573573591703107</v>
       </c>
     </row>
     <row r="123">
@@ -98718,7 +98718,7 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.02833904925417758</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.08013767004013062</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.08482550302227121</v>
+        <v>0.0857357837435978</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.022306959490142</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.01787252724170685</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1010207713046549</v>
+        <v>0.08573587939673126</v>
       </c>
     </row>
     <row r="125">
@@ -100308,7 +100308,7 @@
         <v>0</v>
       </c>
       <c r="IY125" t="n">
-        <v>0.006067602199339704</v>
+        <v>0</v>
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.02051994204521179</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.09078895699654869</v>
+        <v>0.08573575983031444</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.006405674593389435</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.140998438000679</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7705587654005177</v>
+        <v>0.1599999999999997</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.09110552368682599</v>
+        <v>0.08573576780140889</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000001.xlsx
+++ b/out/Attention-mamba2_repeat_2_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.02085027098655701</v>
+        <v>0.02082062512636185</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.5799999999999997</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1831559538841248</v>
+        <v>-0.1831364631652832</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.2999999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.04311823099851608</v>
+        <v>0.04309678822755814</v>
       </c>
       <c r="JB4" t="n">
         <v>0.5799999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.06485386192798615</v>
+        <v>0.06484983861446381</v>
       </c>
       <c r="JB5" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.04271537810564041</v>
+        <v>0.04268713295459747</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.3013719320297241</v>
+        <v>-0.3013216555118561</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.06413553655147552</v>
+        <v>0.06410053372383118</v>
       </c>
       <c r="JB8" t="n">
         <v>0.5799999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.05619759857654572</v>
+        <v>0.05618871748447418</v>
       </c>
       <c r="JB9" t="n">
         <v>0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.01271563023328781</v>
+        <v>0.01270532608032227</v>
       </c>
       <c r="JB10" t="n">
         <v>0.8599999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.07160837948322296</v>
+        <v>0.07160124182701111</v>
       </c>
       <c r="JB11" t="n">
         <v>0.8599999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.03612445294857025</v>
+        <v>0.03611665219068527</v>
       </c>
       <c r="JB12" t="n">
         <v>0.7199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.06658336520195007</v>
+        <v>0.06657034158706665</v>
       </c>
       <c r="JB13" t="n">
         <v>0.5799999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.02548615634441376</v>
+        <v>0.02543306350708008</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.3</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2377505153417587</v>
+        <v>-0.2378295958042145</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.372608482837677</v>
+        <v>-0.3726775944232941</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.4112226963043213</v>
+        <v>-0.4112308323383331</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0059819296002388</v>
+        <v>-0.006104402244091034</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.08042165637016296</v>
+        <v>-0.08049103617668152</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.04262510314583778</v>
+        <v>-0.04269911721348763</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.02000000000000007</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.05348653346300125</v>
+        <v>0.05346547067165375</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.05478795617818832</v>
+        <v>0.05478821694850922</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.03523834049701691</v>
+        <v>0.03522737324237823</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1570518910884857</v>
+        <v>-0.1570772677659988</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2384156137704849</v>
+        <v>-0.2384691387414932</v>
       </c>
       <c r="JB25" t="n">
         <v>0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.04484488070011139</v>
+        <v>0.04478850960731506</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.0259803980588913</v>
+        <v>0.02594180405139923</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.03047862648963928</v>
+        <v>0.03044840693473816</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.02000000000000007</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0708463042974472</v>
+        <v>0.0708322674036026</v>
       </c>
       <c r="JB29" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.03683719038963318</v>
+        <v>0.03681015968322754</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.4481849372386932</v>
+        <v>-0.4481718838214874</v>
       </c>
       <c r="JB31" t="n">
         <v>0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.07608968019485474</v>
+        <v>0.07603621482849121</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.1158312782645226</v>
+        <v>-0.1158727556467056</v>
       </c>
       <c r="JB33" t="n">
         <v>0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0654134601354599</v>
+        <v>0.06538280844688416</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.04499118030071259</v>
+        <v>0.04497253149747849</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.05896298587322235</v>
+        <v>0.05894947052001953</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.03423741459846497</v>
+        <v>0.03421425819396973</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.02798718214035034</v>
+        <v>0.02795529365539551</v>
       </c>
       <c r="JB38" t="n">
         <v>0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.03064344823360443</v>
+        <v>0.03060322254896164</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.3803468644618988</v>
+        <v>-0.3803403079509735</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.241810530424118</v>
+        <v>-0.2416792809963226</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.1723001599311829</v>
+        <v>-0.1720997989177704</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.1150992885231972</v>
+        <v>-0.1147582828998566</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.07241015881299973</v>
+        <v>-0.07217565178871155</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.08281875401735306</v>
+        <v>-0.08274410665035248</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.07068553566932678</v>
+        <v>-0.07063943892717361</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.08051518350839615</v>
+        <v>-0.08052396774291992</v>
       </c>
       <c r="JB47" t="n">
         <v>0.16</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.05367901921272278</v>
+        <v>0.05369437485933304</v>
       </c>
       <c r="JB48" t="n">
         <v>0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.02870155870914459</v>
+        <v>0.02870475500822067</v>
       </c>
       <c r="JB49" t="n">
         <v>0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.07046616077423096</v>
+        <v>0.07047075033187866</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.09345868229866028</v>
+        <v>0.09343469142913818</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1272715479135513</v>
+        <v>0.1273967176675797</v>
       </c>
       <c r="JB52" t="n">
         <v>0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.02761002629995346</v>
+        <v>0.02764014154672623</v>
       </c>
       <c r="JB53" t="n">
         <v>0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0294090136885643</v>
+        <v>-0.02939832210540771</v>
       </c>
       <c r="JB54" t="n">
         <v>0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.1143838465213776</v>
+        <v>0.1143723726272583</v>
       </c>
       <c r="JB55" t="n">
         <v>0.5799999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.1178103387355804</v>
+        <v>0.1176929473876953</v>
       </c>
       <c r="JB56" t="n">
         <v>0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.04790331423282623</v>
+        <v>0.04816528409719467</v>
       </c>
       <c r="JB57" t="n">
         <v>0.2599999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.06429532170295715</v>
+        <v>0.06541666388511658</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.08470404148101807</v>
+        <v>0.08519773185253143</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.09840543568134308</v>
+        <v>0.09859736263751984</v>
       </c>
       <c r="JB60" t="n">
         <v>0.8599999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.1216852515935898</v>
+        <v>0.1216625869274139</v>
       </c>
       <c r="JB61" t="n">
         <v>0.8599999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.116411030292511</v>
+        <v>0.1165873259305954</v>
       </c>
       <c r="JB62" t="n">
         <v>0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.1018993258476257</v>
+        <v>0.1017892062664032</v>
       </c>
       <c r="JB63" t="n">
         <v>0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.100235715508461</v>
+        <v>0.1008474230766296</v>
       </c>
       <c r="JB64" t="n">
         <v>0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.1066407263278961</v>
+        <v>0.1066121459007263</v>
       </c>
       <c r="JB65" t="n">
         <v>0.8599999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1270077228546143</v>
+        <v>0.1271761953830719</v>
       </c>
       <c r="JB66" t="n">
         <v>0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.0304449275135994</v>
+        <v>0.0304558053612709</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.08147308230400085</v>
+        <v>0.08145077526569366</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.02000000000000007</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1258122026920319</v>
+        <v>0.125896081328392</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.09181785583496094</v>
+        <v>0.09171789884567261</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.09137147665023804</v>
+        <v>0.09144461154937744</v>
       </c>
       <c r="JB71" t="n">
         <v>0.1199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.08633142709732056</v>
+        <v>0.08681683242321014</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1124690920114517</v>
+        <v>0.1119251996278763</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.3</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.03986454755067825</v>
+        <v>-0.0397803895175457</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.1600000000000001</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.02382677048444748</v>
+        <v>-0.02383418381214142</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1165706962347031</v>
+        <v>0.1160154044628143</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.5799999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.03962594270706177</v>
+        <v>0.03991812467575073</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.3</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1084654033184052</v>
+        <v>0.1084351688623428</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1023992598056793</v>
+        <v>0.1008972078561783</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.5799999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.006118275225162506</v>
+        <v>0.006063774228096008</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.004271037876605988</v>
+        <v>-0.004254400730133057</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.01938682794570923</v>
+        <v>-0.01945317536592484</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.03338298946619034</v>
+        <v>0.03444712609052658</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.03522747009992599</v>
+        <v>0.03558345139026642</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.06255679577589035</v>
+        <v>0.06360527873039246</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.05047409236431122</v>
+        <v>0.05099820345640182</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.006545256823301315</v>
+        <v>-0.006578847765922546</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.09575867652893066</v>
+        <v>0.09566208720207214</v>
       </c>
       <c r="JB88" t="n">
         <v>0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.07868045568466187</v>
+        <v>0.07933397591114044</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.05306160449981689</v>
+        <v>0.05300740152597427</v>
       </c>
       <c r="JB90" t="n">
         <v>0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.07530277967453003</v>
+        <v>0.07623755931854248</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.04822862893342972</v>
+        <v>0.04859301447868347</v>
       </c>
       <c r="JB92" t="n">
         <v>0.16</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1112610697746277</v>
+        <v>0.111368328332901</v>
       </c>
       <c r="JB93" t="n">
         <v>0.1600000000000001</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.02487679570913315</v>
+        <v>0.0248740017414093</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.005148991942405701</v>
+        <v>-0.005143802613019943</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.03896266222000122</v>
+        <v>0.04020725190639496</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.006210658699274063</v>
+        <v>-0.006300650537014008</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.01430939882993698</v>
+        <v>-0.01424678042531013</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1204110383987427</v>
+        <v>0.1203887313604355</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.1240293830633163</v>
+        <v>0.1238578855991364</v>
       </c>
       <c r="JB100" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.1225882768630981</v>
+        <v>0.1224280297756195</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.07113641500473022</v>
+        <v>0.07105013728141785</v>
       </c>
       <c r="JB102" t="n">
         <v>0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.1047483831644058</v>
+        <v>0.1051546335220337</v>
       </c>
       <c r="JB103" t="n">
         <v>0.8599999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1180445849895477</v>
+        <v>0.1181105822324753</v>
       </c>
       <c r="JB104" t="n">
         <v>0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1306850612163544</v>
+        <v>0.1308745294809341</v>
       </c>
       <c r="JB105" t="n">
         <v>0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.08124767243862152</v>
+        <v>0.08117853105068207</v>
       </c>
       <c r="JB106" t="n">
         <v>0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.1038160175085068</v>
+        <v>0.1026793122291565</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.16</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06852950155735016</v>
+        <v>0.06903649866580963</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002210322767496109</v>
+        <v>-0.002267211675643921</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.04770264029502869</v>
+        <v>0.04972364008426666</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.002155490219593048</v>
+        <v>-0.002238377928733826</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.01735235005617142</v>
+        <v>-0.01737075299024582</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002108506858348846</v>
+        <v>-0.001968163996934891</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.01085083559155464</v>
+        <v>-0.01087186858057976</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.04032652080059052</v>
+        <v>0.04144147038459778</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.02152110636234283</v>
+        <v>0.02156112343072891</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.01768418028950691</v>
+        <v>-0.01777698844671249</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.009849186986684799</v>
+        <v>-0.009825684130191803</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.007919818162918091</v>
+        <v>0.008291490375995636</v>
       </c>
       <c r="JB119" t="n">
         <v>0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.1233797669410706</v>
+        <v>0.1242179721593857</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.08949634432792664</v>
+        <v>0.08936768770217896</v>
       </c>
       <c r="JB121" t="n">
         <v>0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.05687950551509857</v>
+        <v>0.05727039277553558</v>
       </c>
       <c r="JB122" t="n">
         <v>0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.08013767004013062</v>
+        <v>0.08231648802757263</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.01787252724170685</v>
+        <v>0.01787837594747543</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.02051994204521179</v>
+        <v>0.02110147476196289</v>
       </c>
       <c r="JB125" t="n">
         <v>0.2999999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.140998438000679</v>
+        <v>0.1413460522890091</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1599999999999997</v>
